--- a/artfynd/A 62027-2021 artfynd.xlsx
+++ b/artfynd/A 62027-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113126870</v>
       </c>
       <c r="B2" t="n">
-        <v>91333</v>
+        <v>91349</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 62027-2021 artfynd.xlsx
+++ b/artfynd/A 62027-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113126870</v>
       </c>
       <c r="B2" t="n">
-        <v>91349</v>
+        <v>91361</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 62027-2021 artfynd.xlsx
+++ b/artfynd/A 62027-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113126870</v>
       </c>
       <c r="B2" t="n">
-        <v>91361</v>
+        <v>91383</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 62027-2021 artfynd.xlsx
+++ b/artfynd/A 62027-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62027-2021 artfynd.xlsx
+++ b/artfynd/A 62027-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,6 +791,312 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123417470</v>
+      </c>
+      <c r="B3" t="n">
+        <v>95139</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gåshult, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>368880</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6415194</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bredared</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Johan Linderstad, Bo Hultgren, Börje Fritzson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123417463</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57497</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gåshult, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>368870</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6415232</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bredared</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Johan Linderstad, Bo Hultgren, Börje Fritzson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123417462</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96901</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2569</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stor revmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Bazzania trilobata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gåshult, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>368873</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6415266</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bredared</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Johan Linderstad, Bo Hultgren, Börje Fritzson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62027-2021 artfynd.xlsx
+++ b/artfynd/A 62027-2021 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123417470</v>
+        <v>123417463</v>
       </c>
       <c r="B3" t="n">
-        <v>95139</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>368880</v>
+        <v>368870</v>
       </c>
       <c r="R3" t="n">
-        <v>6415194</v>
+        <v>6415232</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123417463</v>
+        <v>123417462</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>96901</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,25 +908,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>368870</v>
+        <v>368873</v>
       </c>
       <c r="R4" t="n">
-        <v>6415232</v>
+        <v>6415266</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123417462</v>
+        <v>123417470</v>
       </c>
       <c r="B5" t="n">
-        <v>96901</v>
+        <v>95139</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>368873</v>
+        <v>368880</v>
       </c>
       <c r="R5" t="n">
-        <v>6415266</v>
+        <v>6415194</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 62027-2021 artfynd.xlsx
+++ b/artfynd/A 62027-2021 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123417463</v>
+        <v>123417470</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>95141</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>368870</v>
+        <v>368880</v>
       </c>
       <c r="R3" t="n">
-        <v>6415232</v>
+        <v>6415194</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,7 +899,7 @@
         <v>123417462</v>
       </c>
       <c r="B4" t="n">
-        <v>96901</v>
+        <v>96903</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123417470</v>
+        <v>123417463</v>
       </c>
       <c r="B5" t="n">
-        <v>95139</v>
+        <v>57497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1010,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>368880</v>
+        <v>368870</v>
       </c>
       <c r="R5" t="n">
-        <v>6415194</v>
+        <v>6415232</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 62027-2021 artfynd.xlsx
+++ b/artfynd/A 62027-2021 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>123417470</v>
       </c>
       <c r="B3" t="n">
-        <v>95141</v>
+        <v>95147</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>123417462</v>
       </c>
       <c r="B4" t="n">
-        <v>96903</v>
+        <v>96909</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 62027-2021 artfynd.xlsx
+++ b/artfynd/A 62027-2021 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123417470</v>
+        <v>123417462</v>
       </c>
       <c r="B3" t="n">
-        <v>95147</v>
+        <v>96912</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>368880</v>
+        <v>368873</v>
       </c>
       <c r="R3" t="n">
-        <v>6415194</v>
+        <v>6415266</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123417462</v>
+        <v>123417470</v>
       </c>
       <c r="B4" t="n">
-        <v>96909</v>
+        <v>95150</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,21 +912,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>368873</v>
+        <v>368880</v>
       </c>
       <c r="R4" t="n">
-        <v>6415266</v>
+        <v>6415194</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 62027-2021 artfynd.xlsx
+++ b/artfynd/A 62027-2021 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>123417462</v>
       </c>
       <c r="B3" t="n">
-        <v>96912</v>
+        <v>96929</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>123417470</v>
       </c>
       <c r="B4" t="n">
-        <v>95150</v>
+        <v>95167</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>123417463</v>
       </c>
       <c r="B5" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 62027-2021 artfynd.xlsx
+++ b/artfynd/A 62027-2021 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123417462</v>
+        <v>123417470</v>
       </c>
       <c r="B3" t="n">
-        <v>96929</v>
+        <v>95173</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>368873</v>
+        <v>368880</v>
       </c>
       <c r="R3" t="n">
-        <v>6415266</v>
+        <v>6415194</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123417470</v>
+        <v>123417462</v>
       </c>
       <c r="B4" t="n">
-        <v>95167</v>
+        <v>96945</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,21 +912,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>368880</v>
+        <v>368873</v>
       </c>
       <c r="R4" t="n">
-        <v>6415194</v>
+        <v>6415266</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,7 +1001,7 @@
         <v>123417463</v>
       </c>
       <c r="B5" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 62027-2021 artfynd.xlsx
+++ b/artfynd/A 62027-2021 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>123417470</v>
       </c>
       <c r="B3" t="n">
-        <v>95173</v>
+        <v>95175</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>123417462</v>
       </c>
       <c r="B4" t="n">
-        <v>96945</v>
+        <v>96947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>123417463</v>
       </c>
       <c r="B5" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 62027-2021 artfynd.xlsx
+++ b/artfynd/A 62027-2021 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123417470</v>
+        <v>123417463</v>
       </c>
       <c r="B3" t="n">
-        <v>95175</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>368880</v>
+        <v>368870</v>
       </c>
       <c r="R3" t="n">
-        <v>6415194</v>
+        <v>6415232</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123417462</v>
+        <v>123417470</v>
       </c>
       <c r="B4" t="n">
-        <v>96947</v>
+        <v>95683</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,21 +912,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>368873</v>
+        <v>368880</v>
       </c>
       <c r="R4" t="n">
-        <v>6415266</v>
+        <v>6415194</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123417463</v>
+        <v>123417462</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>96707</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1010,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>368870</v>
+        <v>368873</v>
       </c>
       <c r="R5" t="n">
-        <v>6415232</v>
+        <v>6415266</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 62027-2021 artfynd.xlsx
+++ b/artfynd/A 62027-2021 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123417463</v>
+        <v>123417462</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>96707</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>368870</v>
+        <v>368873</v>
       </c>
       <c r="R3" t="n">
-        <v>6415232</v>
+        <v>6415266</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123417462</v>
+        <v>123417463</v>
       </c>
       <c r="B5" t="n">
-        <v>96707</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1010,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>368873</v>
+        <v>368870</v>
       </c>
       <c r="R5" t="n">
-        <v>6415266</v>
+        <v>6415232</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 62027-2021 artfynd.xlsx
+++ b/artfynd/A 62027-2021 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123417462</v>
+        <v>123417470</v>
       </c>
       <c r="B3" t="n">
-        <v>96707</v>
+        <v>95683</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>368873</v>
+        <v>368880</v>
       </c>
       <c r="R3" t="n">
-        <v>6415266</v>
+        <v>6415194</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,10 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123417470</v>
+        <v>123417462</v>
       </c>
       <c r="B4" t="n">
-        <v>95683</v>
+        <v>96707</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,21 +912,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>368880</v>
+        <v>368873</v>
       </c>
       <c r="R4" t="n">
-        <v>6415194</v>
+        <v>6415266</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 62027-2021 artfynd.xlsx
+++ b/artfynd/A 62027-2021 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123417470</v>
+        <v>123417463</v>
       </c>
       <c r="B3" t="n">
-        <v>95683</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,25 +806,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>368880</v>
+        <v>368870</v>
       </c>
       <c r="R3" t="n">
-        <v>6415194</v>
+        <v>6415232</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123417463</v>
+        <v>123417470</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>95683</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1010,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>368870</v>
+        <v>368880</v>
       </c>
       <c r="R5" t="n">
-        <v>6415232</v>
+        <v>6415194</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 62027-2021 artfynd.xlsx
+++ b/artfynd/A 62027-2021 artfynd.xlsx
@@ -675,64 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113126870</v>
+        <v>123417470</v>
       </c>
       <c r="B2" t="n">
-        <v>91648</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5448</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bredared 1:4, Vg</t>
+          <t>Gåshult, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>368848</v>
+        <v>368880</v>
       </c>
       <c r="R2" t="n">
-        <v>6415240</v>
+        <v>6415194</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Många fruktkroppar. Fruktkroppar satt gyttrade. Ett mycel? På gammal mossövervuxen myrstack(?). Gran närmast intill. Även lite äldre tall.</t>
+          <t>2025-03-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,34 +754,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Nora Toftgård Shahnavaz</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Nora Toftgård Shahnavaz, Maria  Werner, Johan Linderstad, Bo Hultgren, Börje Fritzson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123417470</v>
+        <v>123417462</v>
       </c>
       <c r="B3" t="n">
-        <v>95705</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>368880</v>
+        <v>368873</v>
       </c>
       <c r="R3" t="n">
-        <v>6415194</v>
+        <v>6415266</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123417463</v>
+        <v>113126870</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,37 +880,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5448</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gåshult, Vg</t>
+          <t>Bredared 1:4, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>368870</v>
+        <v>368848</v>
       </c>
       <c r="R4" t="n">
-        <v>6415232</v>
+        <v>6415240</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -966,12 +945,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2023-10-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-22</t>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Många fruktkroppar. Fruktkroppar satt gyttrade. Ett mycel? På gammal mossövervuxen myrstack(?). Gran närmast intill. Även lite äldre tall.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,33 +964,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Nora Toftgård Shahnavaz, Maria  Werner, Johan Linderstad, Bo Hultgren, Börje Fritzson</t>
+          <t>Lars Gerre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123417462</v>
+        <v>123417463</v>
       </c>
       <c r="B5" t="n">
-        <v>96729</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1014,21 +994,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>368873</v>
+        <v>368870</v>
       </c>
       <c r="R5" t="n">
-        <v>6415266</v>
+        <v>6415232</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 62027-2021 artfynd.xlsx
+++ b/artfynd/A 62027-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123417470</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123417462</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113126870</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,8 +1097,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123417463</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>